--- a/Result/profitability/2442.xlsx
+++ b/Result/profitability/2442.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,7 +672,7 @@
         <v>0.7812499999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>32.16375</v>
+        <v>29.10625</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.8</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6774999999999999</v>
+        <v>0.6475</v>
       </c>
       <c r="N3" t="n">
-        <v>28.92</v>
+        <v>25.5425</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.02</v>
       </c>
       <c r="M4" t="n">
-        <v>0.64625</v>
+        <v>0.6137499999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>25.59125</v>
+        <v>22.3775</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.28</v>
       </c>
       <c r="M5" t="n">
-        <v>0.575</v>
+        <v>0.5475</v>
       </c>
       <c r="N5" t="n">
-        <v>22.3075</v>
+        <v>17.3725</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.49</v>
       </c>
       <c r="M6" t="n">
-        <v>0.605</v>
+        <v>0.5937499999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>17.995</v>
+        <v>11.0675</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.62</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6675</v>
+        <v>0.09624999999999997</v>
       </c>
       <c r="N7" t="n">
-        <v>12.0375</v>
+        <v>8.34125</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.79</v>
       </c>
       <c r="M8" t="n">
-        <v>0.19125</v>
+        <v>0.05249999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>9.18125</v>
+        <v>6.0575</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1403,7 +1403,7 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1518,7 +1518,7 @@
         <v>0.13</v>
       </c>
       <c r="M9" t="n">
-        <v>0.065</v>
+        <v>0.06499999999999999</v>
       </c>
       <c r="N9" t="n">
         <v>6.68375</v>
@@ -1902,7 +1902,7 @@
         <v>0.46</v>
       </c>
       <c r="N12" t="n">
-        <v>7.89</v>
+        <v>7.890000000000001</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2442</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>367</v>
+      </c>
+      <c r="D75" t="n">
+        <v>353</v>
+      </c>
+      <c r="E75" t="n">
+        <v>14</v>
+      </c>
+      <c r="F75" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-35</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-9.45%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>40</v>
+      </c>
+      <c r="J75" t="n">
+        <v>5</v>
+      </c>
+      <c r="K75" t="n">
+        <v>11</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.8412499999999999</v>
+      </c>
+      <c r="N75" t="n">
+        <v>32.19125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-1.11</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.9736842105263158</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-24.99</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.8662045060658579</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.88</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-39.48</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.9109367789570836</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
